--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU02/HRM/pre LAM_HRM-2031-0292/Panel 7/back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU02/HRM/pre LAM_HRM-2031-0292/Panel 7/back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Back_Summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.81802</v>
+        <v>16.90417</v>
       </c>
       <c r="D2" t="n">
-        <v>16.81549</v>
+        <v>16.56252</v>
       </c>
       <c r="E2" t="n">
-        <v>16.60882</v>
+        <v>16.59146</v>
       </c>
       <c r="F2" t="n">
-        <v>42.11307</v>
+        <v>42.86836</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05028</v>
+        <v>0.05074</v>
       </c>
       <c r="H2" t="n">
-        <v>1.8513</v>
+        <v>1.8285</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.90131</v>
+        <v>16.66208</v>
       </c>
       <c r="D3" t="n">
-        <v>16.26059</v>
+        <v>16.41384</v>
       </c>
       <c r="E3" t="n">
-        <v>16.93065</v>
+        <v>16.52694</v>
       </c>
       <c r="F3" t="n">
-        <v>42.48702</v>
+        <v>42.0403</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0499</v>
+        <v>0.05074</v>
       </c>
       <c r="H3" t="n">
-        <v>1.81611</v>
+        <v>1.78753</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.95904</v>
+        <v>16.82332</v>
       </c>
       <c r="D4" t="n">
-        <v>16.72757</v>
+        <v>16.58763</v>
       </c>
       <c r="E4" t="n">
-        <v>17.18961</v>
+        <v>16.76556</v>
       </c>
       <c r="F4" t="n">
-        <v>42.4685</v>
+        <v>42.61208</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04979</v>
+        <v>0.05108</v>
       </c>
       <c r="H4" t="n">
-        <v>1.81613</v>
+        <v>1.86832</v>
       </c>
     </row>
     <row r="5">
@@ -535,22 +535,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.84371</v>
+        <v>17.06602</v>
       </c>
       <c r="D5" t="n">
-        <v>16.71089</v>
+        <v>16.50199</v>
       </c>
       <c r="E5" t="n">
-        <v>16.69901</v>
+        <v>16.69386</v>
       </c>
       <c r="F5" t="n">
-        <v>41.84133</v>
+        <v>43.41146</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05067</v>
+        <v>0.05111</v>
       </c>
       <c r="H5" t="n">
-        <v>1.84795</v>
+        <v>1.81604</v>
       </c>
     </row>
     <row r="6">
@@ -560,22 +560,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.63819</v>
+        <v>16.60601</v>
       </c>
       <c r="D6" t="n">
-        <v>16.61505</v>
+        <v>16.26978</v>
       </c>
       <c r="E6" t="n">
-        <v>16.9588</v>
+        <v>16.41573</v>
       </c>
       <c r="F6" t="n">
-        <v>42.42351</v>
+        <v>42.06126</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05091</v>
+        <v>0.05155</v>
       </c>
       <c r="H6" t="n">
-        <v>1.85146</v>
+        <v>1.83636</v>
       </c>
     </row>
     <row r="7">
@@ -585,22 +585,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.58766</v>
+        <v>16.58372</v>
       </c>
       <c r="D7" t="n">
-        <v>16.64409</v>
+        <v>16.41326</v>
       </c>
       <c r="E7" t="n">
-        <v>17.10338</v>
+        <v>16.56479</v>
       </c>
       <c r="F7" t="n">
-        <v>41.86269</v>
+        <v>42.47038</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05085</v>
+        <v>0.05043</v>
       </c>
       <c r="H7" t="n">
-        <v>1.8315</v>
+        <v>1.84831</v>
       </c>
     </row>
     <row r="8">
@@ -610,22 +610,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.62936</v>
+        <v>16.96352</v>
       </c>
       <c r="D8" t="n">
-        <v>16.90246</v>
+        <v>16.45818</v>
       </c>
       <c r="E8" t="n">
-        <v>16.60697</v>
+        <v>16.49182</v>
       </c>
       <c r="F8" t="n">
-        <v>42.43467</v>
+        <v>42.48364</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05057</v>
+        <v>0.0515</v>
       </c>
       <c r="H8" t="n">
-        <v>1.82627</v>
+        <v>1.83139</v>
       </c>
     </row>
     <row r="9">
@@ -635,22 +635,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.90568</v>
+        <v>17.09567</v>
       </c>
       <c r="D9" t="n">
-        <v>16.46762</v>
+        <v>16.7376</v>
       </c>
       <c r="E9" t="n">
-        <v>16.48431</v>
+        <v>16.85069</v>
       </c>
       <c r="F9" t="n">
-        <v>42.65455</v>
+        <v>42.13432</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05092</v>
+        <v>0.05079</v>
       </c>
       <c r="H9" t="n">
-        <v>1.79307</v>
+        <v>1.83343</v>
       </c>
     </row>
     <row r="10">
@@ -660,22 +660,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16.79047</v>
+        <v>16.85443</v>
       </c>
       <c r="D10" t="n">
-        <v>16.57202</v>
+        <v>16.32601</v>
       </c>
       <c r="E10" t="n">
-        <v>16.72217</v>
+        <v>16.73092</v>
       </c>
       <c r="F10" t="n">
-        <v>42.8057</v>
+        <v>42.53654</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05053</v>
+        <v>0.05054</v>
       </c>
       <c r="H10" t="n">
-        <v>1.80869</v>
+        <v>1.83504</v>
       </c>
     </row>
     <row r="11">
@@ -718,26 +718,26 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Pad 1</t>
+          <t>Pad 2</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>16.7474</v>
+        <v>16.90932</v>
       </c>
       <c r="D12" t="n">
-        <v>16.35144</v>
+        <v>16.59844</v>
       </c>
       <c r="E12" t="n">
-        <v>16.76285</v>
+        <v>16.69888</v>
       </c>
       <c r="F12" t="n">
-        <v>42.05961</v>
+        <v>42.86859</v>
       </c>
       <c r="G12" t="n">
-        <v>0.04957</v>
+        <v>0.05011</v>
       </c>
       <c r="H12" t="n">
-        <v>1.82136</v>
+        <v>1.83952</v>
       </c>
     </row>
     <row r="13">
@@ -747,22 +747,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>16.84471</v>
+        <v>16.78311</v>
       </c>
       <c r="D13" t="n">
-        <v>16.69927</v>
+        <v>16.51133</v>
       </c>
       <c r="E13" t="n">
-        <v>16.83621</v>
+        <v>16.77512</v>
       </c>
       <c r="F13" t="n">
-        <v>43.47545</v>
+        <v>42.131</v>
       </c>
       <c r="G13" t="n">
-        <v>0.05103</v>
+        <v>0.05123</v>
       </c>
       <c r="H13" t="n">
-        <v>1.83155</v>
+        <v>1.83385</v>
       </c>
     </row>
     <row r="14">
@@ -772,22 +772,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>16.89236</v>
+        <v>16.71234</v>
       </c>
       <c r="D14" t="n">
-        <v>16.58211</v>
+        <v>16.67273</v>
       </c>
       <c r="E14" t="n">
-        <v>16.6838</v>
+        <v>16.70155</v>
       </c>
       <c r="F14" t="n">
-        <v>42.58422</v>
+        <v>41.89892</v>
       </c>
       <c r="G14" t="n">
-        <v>0.05014</v>
+        <v>0.04963</v>
       </c>
       <c r="H14" t="n">
-        <v>1.8404</v>
+        <v>1.79388</v>
       </c>
     </row>
     <row r="15">
@@ -797,22 +797,22 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>16.94036</v>
+        <v>17.0966</v>
       </c>
       <c r="D15" t="n">
-        <v>16.72401</v>
+        <v>16.60065</v>
       </c>
       <c r="E15" t="n">
-        <v>16.61838</v>
+        <v>16.81259</v>
       </c>
       <c r="F15" t="n">
-        <v>42.54519</v>
+        <v>41.56518</v>
       </c>
       <c r="G15" t="n">
-        <v>0.05156</v>
+        <v>0.05073</v>
       </c>
       <c r="H15" t="n">
-        <v>1.80729</v>
+        <v>1.79927</v>
       </c>
     </row>
     <row r="16">
@@ -822,22 +822,22 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>16.87311</v>
+        <v>16.51399</v>
       </c>
       <c r="D16" t="n">
-        <v>16.67033</v>
+        <v>16.29966</v>
       </c>
       <c r="E16" t="n">
-        <v>16.68453</v>
+        <v>16.45676</v>
       </c>
       <c r="F16" t="n">
-        <v>42.4034</v>
+        <v>42.79417</v>
       </c>
       <c r="G16" t="n">
-        <v>0.05077</v>
+        <v>0.05034</v>
       </c>
       <c r="H16" t="n">
-        <v>1.83091</v>
+        <v>1.79752</v>
       </c>
     </row>
     <row r="17">
@@ -847,22 +847,22 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>17.07575</v>
+        <v>16.98645</v>
       </c>
       <c r="D17" t="n">
-        <v>16.33089</v>
+        <v>16.39157</v>
       </c>
       <c r="E17" t="n">
-        <v>16.4384</v>
+        <v>16.78674</v>
       </c>
       <c r="F17" t="n">
-        <v>42.60374</v>
+        <v>42.37479</v>
       </c>
       <c r="G17" t="n">
-        <v>0.05034</v>
+        <v>0.05111</v>
       </c>
       <c r="H17" t="n">
-        <v>1.79557</v>
+        <v>1.82971</v>
       </c>
     </row>
     <row r="18">
@@ -872,22 +872,22 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>16.98422</v>
+        <v>16.9014</v>
       </c>
       <c r="D18" t="n">
-        <v>16.63158</v>
+        <v>16.53206</v>
       </c>
       <c r="E18" t="n">
-        <v>16.49245</v>
+        <v>16.63483</v>
       </c>
       <c r="F18" t="n">
-        <v>42.87011</v>
+        <v>41.92647</v>
       </c>
       <c r="G18" t="n">
-        <v>0.05079</v>
+        <v>0.05081</v>
       </c>
       <c r="H18" t="n">
-        <v>1.81474</v>
+        <v>1.78902</v>
       </c>
     </row>
     <row r="19">
@@ -897,22 +897,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>16.75453</v>
+        <v>16.8095</v>
       </c>
       <c r="D19" t="n">
-        <v>16.66019</v>
+        <v>16.31513</v>
       </c>
       <c r="E19" t="n">
-        <v>16.66002</v>
+        <v>16.53677</v>
       </c>
       <c r="F19" t="n">
-        <v>42.3874</v>
+        <v>42.04434</v>
       </c>
       <c r="G19" t="n">
-        <v>0.05014</v>
+        <v>0.04959</v>
       </c>
       <c r="H19" t="n">
-        <v>1.82655</v>
+        <v>1.83368</v>
       </c>
     </row>
     <row r="20">
@@ -922,33 +922,43 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>16.90591</v>
+        <v>16.53864</v>
       </c>
       <c r="D20" t="n">
-        <v>16.72761</v>
+        <v>16.30077</v>
       </c>
       <c r="E20" t="n">
-        <v>16.83462</v>
+        <v>16.32818</v>
       </c>
       <c r="F20" t="n">
-        <v>42.46255</v>
+        <v>43.21946</v>
       </c>
       <c r="G20" t="n">
-        <v>0.05109</v>
+        <v>0.05054</v>
       </c>
       <c r="H20" t="n">
-        <v>1.80585</v>
+        <v>1.82325</v>
       </c>
     </row>
     <row r="21">
       <c r="C21" t="inlineStr">
         <is>
-          <t>Dimple</t>
+          <t>Max Stepheight</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Bump</t>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Radius</t>
         </is>
       </c>
     </row>
@@ -960,14 +970,20 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>via 1</t>
+          <t>SR Pad 1</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.6038</v>
+        <v>15.77784</v>
       </c>
       <c r="D22" t="n">
-        <v>1.11461</v>
+        <v>15.71926</v>
+      </c>
+      <c r="E22" t="n">
+        <v>15.77237</v>
+      </c>
+      <c r="F22" t="n">
+        <v>248.09223</v>
       </c>
     </row>
     <row r="23">
@@ -977,10 +993,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.6017400000000001</v>
+        <v>15.9304</v>
       </c>
       <c r="D23" t="n">
-        <v>1.11962</v>
+        <v>15.4742</v>
+      </c>
+      <c r="E23" t="n">
+        <v>15.7615</v>
+      </c>
+      <c r="F23" t="n">
+        <v>252.84751</v>
       </c>
     </row>
     <row r="24">
@@ -990,10 +1012,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.5909799999999999</v>
+        <v>15.79551</v>
       </c>
       <c r="D24" t="n">
-        <v>1.10561</v>
+        <v>15.48916</v>
+      </c>
+      <c r="E24" t="n">
+        <v>15.61393</v>
+      </c>
+      <c r="F24" t="n">
+        <v>253.48719</v>
       </c>
     </row>
     <row r="25">
@@ -1003,10 +1031,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.60694</v>
+        <v>15.81948</v>
       </c>
       <c r="D25" t="n">
-        <v>1.11825</v>
+        <v>15.49675</v>
+      </c>
+      <c r="E25" t="n">
+        <v>15.65987</v>
+      </c>
+      <c r="F25" t="n">
+        <v>252.23819</v>
       </c>
     </row>
     <row r="26">
@@ -1016,10 +1050,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.5908600000000001</v>
+        <v>15.87489</v>
       </c>
       <c r="D26" t="n">
-        <v>1.12403</v>
+        <v>15.32151</v>
+      </c>
+      <c r="E26" t="n">
+        <v>15.6722</v>
+      </c>
+      <c r="F26" t="n">
+        <v>253.26116</v>
       </c>
     </row>
     <row r="27">
@@ -1029,10 +1069,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.61053</v>
+        <v>15.86524</v>
       </c>
       <c r="D27" t="n">
-        <v>1.11873</v>
+        <v>15.64211</v>
+      </c>
+      <c r="E27" t="n">
+        <v>15.78304</v>
+      </c>
+      <c r="F27" t="n">
+        <v>256.11859</v>
       </c>
     </row>
     <row r="28">
@@ -1042,10 +1088,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.60118</v>
+        <v>15.50612</v>
       </c>
       <c r="D28" t="n">
-        <v>1.1055</v>
+        <v>15.23044</v>
+      </c>
+      <c r="E28" t="n">
+        <v>15.49277</v>
+      </c>
+      <c r="F28" t="n">
+        <v>258.34193</v>
       </c>
     </row>
     <row r="29">
@@ -1055,10 +1107,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.59657</v>
+        <v>15.84978</v>
       </c>
       <c r="D29" t="n">
-        <v>1.12619</v>
+        <v>15.50347</v>
+      </c>
+      <c r="E29" t="n">
+        <v>15.74691</v>
+      </c>
+      <c r="F29" t="n">
+        <v>254.44371</v>
       </c>
     </row>
     <row r="30">
@@ -1068,10 +1126,744 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.60471</v>
+        <v>15.81706</v>
       </c>
       <c r="D30" t="n">
-        <v>1.11931</v>
+        <v>15.46384</v>
+      </c>
+      <c r="E30" t="n">
+        <v>15.61019</v>
+      </c>
+      <c r="F30" t="n">
+        <v>250.6053</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Width</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Space</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Trace 1</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>16.62873</v>
+      </c>
+      <c r="D32" t="n">
+        <v>15.90302</v>
+      </c>
+      <c r="E32" t="n">
+        <v>16.52288</v>
+      </c>
+      <c r="F32" t="n">
+        <v>22.05739</v>
+      </c>
+      <c r="G32" t="n">
+        <v>34.20889</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>16.94154</v>
+      </c>
+      <c r="D33" t="n">
+        <v>15.94919</v>
+      </c>
+      <c r="E33" t="n">
+        <v>16.37114</v>
+      </c>
+      <c r="F33" t="n">
+        <v>21.39154</v>
+      </c>
+      <c r="G33" t="n">
+        <v>34.25162</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>16.65733</v>
+      </c>
+      <c r="D34" t="n">
+        <v>15.96999</v>
+      </c>
+      <c r="E34" t="n">
+        <v>16.40875</v>
+      </c>
+      <c r="F34" t="n">
+        <v>21.61807</v>
+      </c>
+      <c r="G34" t="n">
+        <v>34.22083</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>16.79886</v>
+      </c>
+      <c r="D35" t="n">
+        <v>16.01749</v>
+      </c>
+      <c r="E35" t="n">
+        <v>16.5731</v>
+      </c>
+      <c r="F35" t="n">
+        <v>21.64633</v>
+      </c>
+      <c r="G35" t="n">
+        <v>33.88969</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>16.79897</v>
+      </c>
+      <c r="D36" t="n">
+        <v>15.82787</v>
+      </c>
+      <c r="E36" t="n">
+        <v>16.36906</v>
+      </c>
+      <c r="F36" t="n">
+        <v>21.56796</v>
+      </c>
+      <c r="G36" t="n">
+        <v>34.51566</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>16.96058</v>
+      </c>
+      <c r="D37" t="n">
+        <v>15.79082</v>
+      </c>
+      <c r="E37" t="n">
+        <v>16.50584</v>
+      </c>
+      <c r="F37" t="n">
+        <v>21.56551</v>
+      </c>
+      <c r="G37" t="n">
+        <v>34.11762</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>16.93997</v>
+      </c>
+      <c r="D38" t="n">
+        <v>15.8368</v>
+      </c>
+      <c r="E38" t="n">
+        <v>15.93684</v>
+      </c>
+      <c r="F38" t="n">
+        <v>21.76996</v>
+      </c>
+      <c r="G38" t="n">
+        <v>34.01423</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>16.58667</v>
+      </c>
+      <c r="D39" t="n">
+        <v>16.28148</v>
+      </c>
+      <c r="E39" t="n">
+        <v>16.38739</v>
+      </c>
+      <c r="F39" t="n">
+        <v>22.10661</v>
+      </c>
+      <c r="G39" t="n">
+        <v>34.20408</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>16.6256</v>
+      </c>
+      <c r="D40" t="n">
+        <v>15.9626</v>
+      </c>
+      <c r="E40" t="n">
+        <v>16.42783</v>
+      </c>
+      <c r="F40" t="n">
+        <v>21.78128</v>
+      </c>
+      <c r="G40" t="n">
+        <v>33.89095</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Width</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Space</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Trace 2</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>16.64173</v>
+      </c>
+      <c r="D42" t="n">
+        <v>15.96222</v>
+      </c>
+      <c r="E42" t="n">
+        <v>16.45304</v>
+      </c>
+      <c r="F42" t="n">
+        <v>21.67411</v>
+      </c>
+      <c r="G42" t="n">
+        <v>34.21465</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>16.59829</v>
+      </c>
+      <c r="D43" t="n">
+        <v>16.10343</v>
+      </c>
+      <c r="E43" t="n">
+        <v>16.59782</v>
+      </c>
+      <c r="F43" t="n">
+        <v>21.73482</v>
+      </c>
+      <c r="G43" t="n">
+        <v>34.53357</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>16.56058</v>
+      </c>
+      <c r="D44" t="n">
+        <v>15.74574</v>
+      </c>
+      <c r="E44" t="n">
+        <v>16.51367</v>
+      </c>
+      <c r="F44" t="n">
+        <v>21.97832</v>
+      </c>
+      <c r="G44" t="n">
+        <v>33.92016</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>16.42363</v>
+      </c>
+      <c r="D45" t="n">
+        <v>16.25954</v>
+      </c>
+      <c r="E45" t="n">
+        <v>16.33332</v>
+      </c>
+      <c r="F45" t="n">
+        <v>21.69591</v>
+      </c>
+      <c r="G45" t="n">
+        <v>33.87646</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>16.70202</v>
+      </c>
+      <c r="D46" t="n">
+        <v>15.86597</v>
+      </c>
+      <c r="E46" t="n">
+        <v>16.60511</v>
+      </c>
+      <c r="F46" t="n">
+        <v>21.67724</v>
+      </c>
+      <c r="G46" t="n">
+        <v>34.05337</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>16.70819</v>
+      </c>
+      <c r="D47" t="n">
+        <v>16.12052</v>
+      </c>
+      <c r="E47" t="n">
+        <v>16.31819</v>
+      </c>
+      <c r="F47" t="n">
+        <v>21.48841</v>
+      </c>
+      <c r="G47" t="n">
+        <v>33.90974</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>17.19077</v>
+      </c>
+      <c r="D48" t="n">
+        <v>16.15388</v>
+      </c>
+      <c r="E48" t="n">
+        <v>16.76451</v>
+      </c>
+      <c r="F48" t="n">
+        <v>22.03024</v>
+      </c>
+      <c r="G48" t="n">
+        <v>34.00325</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>16.89998</v>
+      </c>
+      <c r="D49" t="n">
+        <v>15.65421</v>
+      </c>
+      <c r="E49" t="n">
+        <v>16.58369</v>
+      </c>
+      <c r="F49" t="n">
+        <v>21.44146</v>
+      </c>
+      <c r="G49" t="n">
+        <v>33.8249</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>16.56848</v>
+      </c>
+      <c r="D50" t="n">
+        <v>15.86574</v>
+      </c>
+      <c r="E50" t="n">
+        <v>16.30629</v>
+      </c>
+      <c r="F50" t="n">
+        <v>22.41276</v>
+      </c>
+      <c r="G50" t="n">
+        <v>34.27473</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>via 1</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>0.60051</v>
+      </c>
+      <c r="D52" t="n">
+        <v>1.12281</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>0.61411</v>
+      </c>
+      <c r="D53" t="n">
+        <v>1.12324</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>0.60354</v>
+      </c>
+      <c r="D54" t="n">
+        <v>1.12036</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>0.59319</v>
+      </c>
+      <c r="D55" t="n">
+        <v>1.12912</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>0.60009</v>
+      </c>
+      <c r="D56" t="n">
+        <v>1.12908</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>0.60837</v>
+      </c>
+      <c r="D57" t="n">
+        <v>1.13165</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>0.60475</v>
+      </c>
+      <c r="D58" t="n">
+        <v>1.11259</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>0.61172</v>
+      </c>
+      <c r="D59" t="n">
+        <v>1.1363</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>0.61292</v>
+      </c>
+      <c r="D60" t="n">
+        <v>1.11001</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>via 2</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>0.62022</v>
+      </c>
+      <c r="D62" t="n">
+        <v>1.09804</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>0.60076</v>
+      </c>
+      <c r="D63" t="n">
+        <v>1.13517</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>0.6123</v>
+      </c>
+      <c r="D64" t="n">
+        <v>1.11676</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>0.60923</v>
+      </c>
+      <c r="D65" t="n">
+        <v>1.08363</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>0.60019</v>
+      </c>
+      <c r="D66" t="n">
+        <v>1.13065</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>0.59895</v>
+      </c>
+      <c r="D67" t="n">
+        <v>1.10512</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>0.6127</v>
+      </c>
+      <c r="D68" t="n">
+        <v>1.0974</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>0.59838</v>
+      </c>
+      <c r="D69" t="n">
+        <v>1.10129</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>0.61211</v>
+      </c>
+      <c r="D70" t="n">
+        <v>1.09149</v>
       </c>
     </row>
   </sheetData>
